--- a/data-raw/usgs/usgs_historical_backup.xlsx
+++ b/data-raw/usgs/usgs_historical_backup.xlsx
@@ -19242,13 +19242,13 @@
         <v>142</v>
       </c>
       <c r="C1083" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1083" t="n">
         <v>2009</v>
       </c>
       <c r="E1083" t="n">
-        <v>155</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1084">
@@ -19259,13 +19259,13 @@
         <v>142</v>
       </c>
       <c r="C1084" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1084" t="n">
         <v>2010</v>
       </c>
       <c r="E1084" t="n">
-        <v>158</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1085">
@@ -19276,13 +19276,13 @@
         <v>142</v>
       </c>
       <c r="C1085" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1085" t="n">
         <v>2011</v>
       </c>
       <c r="E1085" t="n">
-        <v>163</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1086">
@@ -19293,13 +19293,13 @@
         <v>142</v>
       </c>
       <c r="C1086" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1086" t="n">
         <v>2012</v>
       </c>
       <c r="E1086" t="n">
-        <v>169</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1087">
@@ -19310,13 +19310,13 @@
         <v>142</v>
       </c>
       <c r="C1087" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1087" t="n">
         <v>2013</v>
       </c>
       <c r="E1087" t="n">
-        <v>175</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1088">
@@ -19327,13 +19327,13 @@
         <v>142</v>
       </c>
       <c r="C1088" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1088" t="n">
         <v>2014</v>
       </c>
       <c r="E1088" t="n">
-        <v>134</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1089">
@@ -19344,13 +19344,13 @@
         <v>142</v>
       </c>
       <c r="C1089" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1089" t="n">
         <v>2015</v>
       </c>
       <c r="E1089" t="n">
-        <v>134</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1090">
@@ -19361,13 +19361,13 @@
         <v>142</v>
       </c>
       <c r="C1090" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1090" t="n">
         <v>2016</v>
       </c>
       <c r="E1090" t="n">
-        <v>107</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1091">
@@ -19378,13 +19378,13 @@
         <v>142</v>
       </c>
       <c r="C1091" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1091" t="n">
         <v>2017</v>
       </c>
       <c r="E1091" t="n">
-        <v>132</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1092">
@@ -19395,13 +19395,13 @@
         <v>142</v>
       </c>
       <c r="C1092" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1092" t="n">
         <v>2018</v>
       </c>
       <c r="E1092" t="n">
-        <v>132</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1093">
@@ -19412,13 +19412,13 @@
         <v>142</v>
       </c>
       <c r="C1093" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1093" t="n">
         <v>2019</v>
       </c>
       <c r="E1093" t="n">
-        <v>134</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1094">
@@ -19429,13 +19429,13 @@
         <v>142</v>
       </c>
       <c r="C1094" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D1094" t="n">
         <v>2020</v>
       </c>
       <c r="E1094" t="n">
-        <v>134</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="1095">
